--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_4_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_4_IN_Piura.xlsx
@@ -1795,7 +1795,7 @@
       </c>
       <c r="C10" s="30">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>71.75</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="C11" s="21">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>19.02</v>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>7.94</v>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="C13" s="21">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>0.98</v>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>0.3</v>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
@@ -1912,11 +1912,11 @@
       </c>
       <c r="B15" s="43">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>230.0983</v>
       </c>
       <c r="C15" s="44">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>99.99</v>
       </c>
       <c r="D15" s="42" t="inlineStr">
         <is>
@@ -1937,11 +1937,11 @@
       </c>
       <c r="B16" s="46">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>208.8701</v>
       </c>
       <c r="C16" s="47">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>90.77</v>
       </c>
       <c r="D16" s="45" t="inlineStr">
         <is>
@@ -1962,11 +1962,11 @@
       </c>
       <c r="B17" s="46">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>21.2282</v>
       </c>
       <c r="C17" s="47">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>9.23</v>
       </c>
       <c r="D17" s="45" t="inlineStr">
         <is>
@@ -2160,11 +2160,11 @@
       </c>
       <c r="B29" s="22">
         <f>SUM(B25:B28)</f>
-        <v/>
+        <v>230.1426</v>
       </c>
       <c r="C29" s="23">
         <f>SUM(C25:C28)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D29" s="17" t="inlineStr"/>
       <c r="E29" s="17" t="inlineStr"/>
@@ -2283,6 +2283,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2684,6 +2685,7 @@
       <c r="F22" s="17" t="inlineStr"/>
       <c r="G22" s="17" t="inlineStr"/>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
@@ -2728,6 +2730,7 @@
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
     </row>
+    <row r="26"/>
     <row r="27" ht="120" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
         <is>
@@ -2980,11 +2983,11 @@
       </c>
       <c r="B13" s="32">
         <f>SUM(B10:B12)</f>
-        <v/>
+        <v>527.72</v>
       </c>
       <c r="C13" s="23">
         <f>SUM(C10:C12)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
@@ -2994,19 +2997,19 @@
       <c r="E13" s="17" t="inlineStr"/>
       <c r="F13" s="17">
         <f>ROUND(AVERAGE(F10:F12),2)</f>
-        <v/>
+        <v>27.57</v>
       </c>
       <c r="G13" s="22">
         <f>ROUND(AVERAGE(G10:G12),4)</f>
-        <v/>
+        <v>0.4547</v>
       </c>
       <c r="H13" s="23">
         <f>ROUND(AVERAGE(H10:H12),2)</f>
-        <v/>
+        <v>31.45</v>
       </c>
       <c r="I13" s="23">
         <f>ROUND(AVERAGE(I10:I12),2)</f>
-        <v/>
+        <v>68.55</v>
       </c>
     </row>
     <row r="14"/>
